--- a/BS_results.xlsx
+++ b/BS_results.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="321">
   <si>
     <t>run</t>
   </si>
@@ -65,7 +65,7 @@
     <t>bs_time</t>
   </si>
   <si>
-    <t>solv%</t>
+    <t>%solv</t>
   </si>
   <si>
     <t>mean</t>
@@ -728,30 +728,54 @@
     <t>92.9</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">0: 1e-2, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>150</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 1e-3, 550: 1e-4</t>
+    </r>
+  </si>
+  <si>
+    <t>52.05</t>
+  </si>
+  <si>
+    <t>50.27</t>
+  </si>
+  <si>
+    <t>52.02</t>
+  </si>
+  <si>
+    <t>20m59s</t>
+  </si>
+  <si>
+    <t>1h55m</t>
+  </si>
+  <si>
+    <t>280.64</t>
+  </si>
+  <si>
+    <t>61.17</t>
+  </si>
+  <si>
     <t>0: 1e-2, 150: 1e-3, 550: 1e-4</t>
   </si>
   <si>
-    <t>52.05</t>
-  </si>
-  <si>
-    <t>50.27</t>
-  </si>
-  <si>
-    <t>52.02</t>
-  </si>
-  <si>
-    <t>20m59s</t>
-  </si>
-  <si>
-    <t>1h55m</t>
-  </si>
-  <si>
-    <t>280.64</t>
-  </si>
-  <si>
-    <t>61.17</t>
-  </si>
-  <si>
     <t>51.85</t>
   </si>
   <si>
@@ -839,7 +863,7 @@
     <t>123.13</t>
   </si>
   <si>
-    <t>ep50optimFast</t>
+    <t>ep50optimFast 0: 1e-1,  3: 6e-2, 5: 4e-2, 10: 2e-2, 30: 1e-2, 50: 8e-3, 100: 4e-3, 150: 1e-3, 550: 1e-4</t>
   </si>
   <si>
     <t>48.82</t>
@@ -860,7 +884,7 @@
     <t>181.50</t>
   </si>
   <si>
-    <t>optim</t>
+    <t>optim { 0: 1e-1, 5: 6e-2,  10: 4e-2, 20: 2e-2, 40: 1e-2, 150:1e-3, 550:1e-4,}</t>
   </si>
   <si>
     <t>52.79</t>
@@ -881,7 +905,7 @@
     <t>70.69</t>
   </si>
   <si>
-    <t>multi_input</t>
+    <t>"input": {0: 1e-1, 5: 6e-2, 10: 1e-2, 20: 6e-3, 50: 1e-3, 550: 1e-4},  optim { 0: 1e-1, 5: 6e-2,  10: 4e-2, 20: 2e-2, 40: 1e-1, 150:1e-3, 550:1e-4,}</t>
   </si>
   <si>
     <t>54.40</t>
@@ -902,7 +926,91 @@
     <t>165.29</t>
   </si>
   <si>
-    <t>3.76M</t>
+    <t>optim {0: 4e-2, 5: 2e-2, 30: 1e-2, 150: 1e-3, 550: 1e-4}</t>
+  </si>
+  <si>
+    <t>49.90</t>
+  </si>
+  <si>
+    <t>48.03</t>
+  </si>
+  <si>
+    <t>52.09</t>
+  </si>
+  <si>
+    <t>20m1s</t>
+  </si>
+  <si>
+    <t>307.74</t>
+  </si>
+  <si>
+    <t>77.61</t>
+  </si>
+  <si>
+    <t>"input": {0: 6e-3, 150: 1e-3, 550: 1e-4}, optim {0: 4e-2, 5: 2e-2, 30: 1e-2, 150: 1e-3, 550: 1e-4}</t>
+  </si>
+  <si>
+    <t>48.33</t>
+  </si>
+  <si>
+    <t>47.81</t>
+  </si>
+  <si>
+    <t>51.21</t>
+  </si>
+  <si>
+    <t>20m53s</t>
+  </si>
+  <si>
+    <t>2h45m</t>
+  </si>
+  <si>
+    <t>336.52</t>
+  </si>
+  <si>
+    <t>110.63</t>
+  </si>
+  <si>
+    <t>optim {0: 2e-2, 20: 1e-2, 150: 1e-3, 550: 1e-4}</t>
+  </si>
+  <si>
+    <t>50.80</t>
+  </si>
+  <si>
+    <t>51.64</t>
+  </si>
+  <si>
+    <t>51.56</t>
+  </si>
+  <si>
+    <t>21m50s</t>
+  </si>
+  <si>
+    <t>297.08</t>
+  </si>
+  <si>
+    <t>69.49</t>
+  </si>
+  <si>
+    <t>"input": {0: 2e-2,  1: 6e-3, 150: 1e-3, 550: 1e-4}, optim {0: 2e-2, 20: 1e-2, 150: 1e-3, 550: 1e-4}</t>
+  </si>
+  <si>
+    <t>50.21</t>
+  </si>
+  <si>
+    <t>51.22</t>
+  </si>
+  <si>
+    <t>21m48s</t>
+  </si>
+  <si>
+    <t>2h17m</t>
+  </si>
+  <si>
+    <t>331.30</t>
+  </si>
+  <si>
+    <t>103.89</t>
   </si>
 </sst>
 </file>
@@ -917,10 +1025,23 @@
     <numFmt numFmtId="178" formatCode="mmm\.yy"/>
     <numFmt numFmtId="179" formatCode="0\.00_);[Red]\(0\.00\)"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="-0.25"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1070,12 +1191,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1390,58 +1523,52 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1453,93 +1580,105 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" quotePrefix="1">
@@ -2070,388 +2209,388 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T42"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.0909090909091" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.81818181818182" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6" style="2" customWidth="1"/>
-    <col min="4" max="4" width="24.7272727272727" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.3636363636364" style="2" customWidth="1"/>
-    <col min="6" max="10" width="8.72727272727273" style="2"/>
-    <col min="11" max="11" width="9.72727272727273" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="8.72727272727273" style="2"/>
+    <col min="1" max="1" width="15.0909090909091" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.81818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7272727272727" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.3636363636364" style="1" customWidth="1"/>
+    <col min="6" max="10" width="8.72727272727273" style="1"/>
+    <col min="11" max="11" width="9.72727272727273" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>157</v>
       </c>
-      <c r="B2" s="2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>1000</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>999</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="1">
         <v>98</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>190</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>566</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="1">
         <v>439667</v>
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>158</v>
       </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>500</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>499</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="G3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="1">
         <v>84</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>257</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>955</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T3" s="2">
+      <c r="T3" s="1">
         <v>463346</v>
       </c>
     </row>
     <row r="4" spans="1:20">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>159</v>
       </c>
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>750</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>749</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="1">
         <v>95</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="O4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>170</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>992</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="R4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="S4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T4" s="2">
+      <c r="T4" s="1">
         <v>450292</v>
       </c>
     </row>
     <row r="5" spans="1:20">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>160</v>
       </c>
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>650</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>649</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="1">
         <v>61</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="O5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>226</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>935</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="R5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="S5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T5" s="2">
+      <c r="T5" s="1">
         <v>474563</v>
       </c>
     </row>
     <row r="6" spans="1:20">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>161</v>
       </c>
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>1000</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>999</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="G6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="1">
         <v>96</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>230</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>767</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="R6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="4" t="s">
+      <c r="S6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T6" s="2">
+      <c r="T6" s="1">
         <v>444283</v>
       </c>
     </row>
@@ -2462,10 +2601,10 @@
       <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="9" t="s">
         <v>63</v>
       </c>
       <c r="E7" s="1">
@@ -2510,7 +2649,7 @@
       <c r="R7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S7" s="5" t="s">
+      <c r="S7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="1">
@@ -2518,1391 +2657,1429 @@
       </c>
     </row>
     <row r="8" spans="1:20">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>167</v>
       </c>
-      <c r="B8" s="2">
-        <v>1</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>500</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>499</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="G8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R8" s="2" t="s">
+      <c r="L8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S8" s="4" t="s">
+      <c r="S8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="T8" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:20">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>167</v>
       </c>
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>500</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>379</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="2" t="s">
+      <c r="G9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="2">
+      <c r="K9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="1">
         <v>100</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="O9" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S9" s="4" t="s">
+      <c r="P9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="T9" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:20">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>167</v>
       </c>
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>500</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>353</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="2" t="s">
+      <c r="G10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="2">
+      <c r="K10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="1">
         <v>90</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="O10" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S10" s="4" t="s">
+      <c r="P10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T10" s="2" t="s">
+      <c r="T10" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:20">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>167</v>
       </c>
-      <c r="B11" s="2">
-        <v>1</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>500</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>288</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="2" t="s">
+      <c r="G11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="2">
+      <c r="K11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="1">
         <v>80</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="O11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S11" s="4" t="s">
+      <c r="P11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T11" s="2" t="s">
+      <c r="T11" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>168</v>
       </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>400</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>399</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S12" s="4" t="s">
+      <c r="L12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T12" s="2" t="s">
+      <c r="T12" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:20">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>168</v>
       </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>400</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>359</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="2" t="s">
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" s="2">
+      <c r="K13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="1">
         <v>50</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="N13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="O13" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S13" s="4" t="s">
+      <c r="P13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T13" s="2" t="s">
+      <c r="T13" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:20">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>168</v>
       </c>
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>400</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <v>303</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="2" t="s">
+      <c r="G14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="2">
+      <c r="K14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="1">
         <v>60</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="N14" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="O14" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S14" s="4" t="s">
+      <c r="P14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T14" s="2" t="s">
+      <c r="T14" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:20">
-      <c r="A15" s="2">
+      <c r="A15" s="4">
         <v>168</v>
       </c>
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6" t="s">
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>400</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <v>315</v>
       </c>
-      <c r="G15" s="2">
-        <v>1</v>
-      </c>
-      <c r="I15" s="2" t="s">
+      <c r="G15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="2">
+      <c r="K15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="1">
         <v>20</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="N15" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="O15" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S15" s="4" t="s">
+      <c r="P15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T15" s="2" t="s">
+      <c r="T15" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>211</v>
       </c>
-      <c r="B16" s="2">
-        <v>1</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="1">
         <v>600</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <v>599</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="1">
         <v>0</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="L16" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16" s="1">
         <v>100</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="N16" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="O16" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>190</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="1">
         <v>955</v>
       </c>
-      <c r="R16" s="2" t="s">
+      <c r="R16" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="S16" s="4" t="s">
+      <c r="S16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T16" s="2">
+      <c r="T16" s="1">
         <v>442525</v>
       </c>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>213</v>
       </c>
-      <c r="B17" s="2">
-        <v>1</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="1">
         <v>600</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>599</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="1">
         <v>0</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K17" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="L17" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M17" s="1">
         <v>97</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="N17" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="O17" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>219</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>652</v>
       </c>
-      <c r="R17" s="2" t="s">
+      <c r="R17" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="S17" s="4" t="s">
+      <c r="S17" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T17" s="2">
+      <c r="T17" s="1">
         <v>446324</v>
       </c>
     </row>
     <row r="18" spans="1:20">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>214</v>
       </c>
-      <c r="B18" s="2">
-        <v>1</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>600</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="1">
         <v>599</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="1">
         <v>0</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="L18" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="M18" s="2">
+      <c r="M18" s="1">
         <v>99</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="N18" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="O18" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>214</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>706</v>
       </c>
-      <c r="R18" s="2" t="s">
+      <c r="R18" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="S18" s="4" t="s">
+      <c r="S18" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T18" s="2">
+      <c r="T18" s="1">
         <v>443230</v>
       </c>
     </row>
     <row r="19" spans="1:20">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>215</v>
       </c>
-      <c r="B19" s="2">
-        <v>1</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="1">
         <v>600</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="1">
         <v>599</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="1">
         <v>0</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="K19" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="L19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M19" s="2">
+      <c r="M19" s="1">
         <v>99</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="N19" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="O19" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>184</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>611</v>
       </c>
-      <c r="R19" s="2" t="s">
+      <c r="R19" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="S19" s="4" t="s">
+      <c r="S19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T19" s="2">
+      <c r="T19" s="1">
         <v>439581</v>
       </c>
     </row>
     <row r="20" spans="1:20">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>218</v>
       </c>
-      <c r="B20" s="2">
-        <v>1</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="B20" s="1">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1">
         <v>600</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="1">
         <v>599</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="1">
         <v>0</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="I20" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="K20" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="L20" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="M20" s="2">
+      <c r="M20" s="1">
         <v>100</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="N20" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="O20" s="2" t="s">
+      <c r="O20" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>207</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>684</v>
       </c>
-      <c r="R20" s="2" t="s">
+      <c r="R20" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="S20" s="4" t="s">
+      <c r="S20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T20" s="2">
+      <c r="T20" s="1">
         <v>436480</v>
       </c>
     </row>
     <row r="21" spans="1:20">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>218</v>
       </c>
-      <c r="B21" s="2">
-        <v>1</v>
-      </c>
-      <c r="D21" s="6" t="s">
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="1">
         <v>600</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="1">
         <v>478</v>
       </c>
-      <c r="G21" s="2">
-        <v>1</v>
-      </c>
-      <c r="I21" s="2" t="s">
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="K21" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="L21" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="M21" s="2">
+      <c r="M21" s="1">
         <v>100</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="N21" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="O21" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>167</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>610</v>
       </c>
-      <c r="R21" s="2" t="s">
+      <c r="R21" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="S21" s="4" t="s">
+      <c r="S21" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T21" s="2">
+      <c r="T21" s="1">
         <v>437115</v>
       </c>
     </row>
     <row r="22" spans="1:20">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>218</v>
       </c>
-      <c r="B22" s="2">
-        <v>1</v>
-      </c>
-      <c r="D22" s="6" t="s">
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="1">
         <v>600</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="1">
         <v>449</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="1">
         <v>0</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="I22" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="K22" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="L22" s="2" t="s">
+      <c r="L22" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="M22" s="2">
+      <c r="M22" s="1">
         <v>100</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="N22" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="O22" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>196</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>917</v>
       </c>
-      <c r="R22" s="2" t="s">
+      <c r="R22" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="S22" s="4" t="s">
+      <c r="S22" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T22" s="2">
+      <c r="T22" s="1">
         <v>438378</v>
       </c>
     </row>
     <row r="23" spans="1:20">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>218</v>
       </c>
-      <c r="B23" s="2">
-        <v>1</v>
-      </c>
-      <c r="D23" s="6" t="s">
+      <c r="B23" s="1">
+        <v>1</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="1">
         <v>600</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="1">
         <v>407</v>
       </c>
-      <c r="G23" s="2">
-        <v>1</v>
-      </c>
-      <c r="I23" s="2" t="s">
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J23" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="K23" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="L23" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M23" s="2">
+      <c r="M23" s="1">
         <v>99</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="N23" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="O23" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>199</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>642</v>
       </c>
-      <c r="R23" s="2" t="s">
+      <c r="R23" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="S23" s="4" t="s">
+      <c r="S23" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T23" s="2">
+      <c r="T23" s="1">
         <v>442717</v>
       </c>
     </row>
     <row r="24" spans="1:20">
-      <c r="A24" s="2">
+      <c r="A24" s="1">
         <v>229</v>
       </c>
-      <c r="B24" s="2">
-        <v>1</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="B24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="1">
         <v>300</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="1">
         <v>193</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="1">
         <v>0</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="I24" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="J24" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="K24" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="L24" s="2" t="s">
+      <c r="L24" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="M24" s="2">
+      <c r="M24" s="1">
         <v>24</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="N24" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="O24" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>363</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>984</v>
       </c>
-      <c r="S24" s="4" t="s">
+      <c r="S24" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T24" s="2">
+      <c r="T24" s="1">
         <v>492368</v>
       </c>
     </row>
     <row r="25" spans="1:20">
-      <c r="A25" s="2">
+      <c r="A25" s="1">
         <v>231</v>
       </c>
-      <c r="B25" s="2">
-        <v>1</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="1">
         <v>300</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="1">
         <v>240</v>
       </c>
-      <c r="G25" s="2">
-        <v>1</v>
-      </c>
-      <c r="H25" s="2" t="s">
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="J25" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="K25" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="L25" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="M25" s="2">
+      <c r="M25" s="1">
         <v>97</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="N25" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="O25" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>215</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>994</v>
       </c>
-      <c r="R25" s="2" t="s">
+      <c r="R25" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="S25" s="4" t="s">
+      <c r="S25" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T25" s="2">
+      <c r="T25" s="1">
         <v>448855</v>
       </c>
     </row>
     <row r="26" spans="1:20">
-      <c r="A26" s="2">
+      <c r="A26" s="1">
         <v>233</v>
       </c>
-      <c r="B26" s="2">
-        <v>1</v>
-      </c>
-      <c r="C26" s="6" t="s">
+      <c r="B26" s="1">
+        <v>1</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="1">
         <v>1000</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="1">
         <v>924</v>
       </c>
-      <c r="G26" s="2">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2" t="s">
+      <c r="G26" s="1">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="I26" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J26" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="K26" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="L26" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="M26" s="2">
+      <c r="M26" s="1">
         <v>99</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="N26" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="O26" s="2" t="s">
+      <c r="O26" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>180</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>840</v>
       </c>
-      <c r="R26" s="2" t="s">
+      <c r="R26" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S26" s="4" t="s">
+      <c r="S26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T26" s="2">
+      <c r="T26" s="1">
         <v>440696</v>
       </c>
     </row>
     <row r="27" spans="1:20">
-      <c r="A27" s="2">
+      <c r="A27" s="1">
         <v>234</v>
       </c>
-      <c r="B27" s="2">
-        <v>1</v>
-      </c>
-      <c r="C27" s="6" t="s">
+      <c r="B27" s="1">
+        <v>1</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>1000</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="1">
         <v>994</v>
       </c>
-      <c r="G27" s="2">
-        <v>1</v>
-      </c>
-      <c r="H27" s="2" t="s">
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="I27" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="J27" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="K27" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="L27" s="2" t="s">
+      <c r="L27" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="M27" s="2">
+      <c r="M27" s="1">
         <v>90</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="N27" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="O27" s="2" t="s">
+      <c r="O27" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>216</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>992</v>
       </c>
-      <c r="R27" s="2" t="s">
+      <c r="R27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="S27" s="4" t="s">
+      <c r="S27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T27" s="2">
+      <c r="T27" s="1">
         <v>454836</v>
       </c>
     </row>
     <row r="28" spans="1:20">
-      <c r="A28" s="2">
+      <c r="A28" s="1">
         <v>235</v>
       </c>
-      <c r="B28" s="2">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="B28" s="1">
+        <v>1</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="1">
         <v>300</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="1">
         <v>289</v>
       </c>
-      <c r="G28" s="2">
-        <v>1</v>
-      </c>
-      <c r="H28" s="2" t="s">
+      <c r="G28" s="1">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="I28" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="J28" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="K28" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="L28" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="M28" s="2">
+      <c r="M28" s="1">
         <v>13</v>
       </c>
-      <c r="N28" s="2" t="s">
+      <c r="N28" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="O28" s="2" t="s">
+      <c r="O28" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>307</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>959</v>
       </c>
-      <c r="R28" s="2" t="s">
+      <c r="R28" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="S28" s="4" t="s">
+      <c r="S28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T28" s="2">
+      <c r="T28" s="1">
         <v>495931</v>
       </c>
     </row>
     <row r="29" spans="1:20">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B29" s="2">
-        <v>1</v>
-      </c>
-      <c r="E29" s="2">
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
         <v>600</v>
       </c>
-      <c r="F29" s="2">
-        <v>599</v>
-      </c>
-      <c r="S29" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="T29" s="2" t="s">
+      <c r="F29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T29" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:20">
-      <c r="A30" s="1">
+      <c r="A30" s="5">
         <v>254</v>
       </c>
-      <c r="B30" s="2">
-        <v>1</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="B30" s="5">
+        <v>1</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="5">
         <v>600</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="5">
         <v>599</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30" s="5">
         <v>0</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="I30" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="J30" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="K30" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="L30" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="M30" s="2">
+      <c r="M30" s="5">
         <v>100</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="N30" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="O30" s="2" t="s">
+      <c r="O30" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="P30" s="2">
+      <c r="P30" s="5">
         <v>172</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30" s="5">
         <v>943</v>
       </c>
-      <c r="R30" s="2" t="s">
+      <c r="R30" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="S30" s="4" t="s">
+      <c r="S30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T30" s="2">
+      <c r="T30" s="1">
         <v>436708</v>
       </c>
     </row>
     <row r="31" spans="1:20">
-      <c r="A31" s="2">
+      <c r="A31" s="5">
         <v>244</v>
       </c>
-      <c r="B31" s="2">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="B31" s="5">
+        <v>1</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="5">
         <v>600</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="5">
         <v>598</v>
       </c>
-      <c r="G31" s="2">
-        <v>1</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="G31" s="5">
+        <v>1</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="I31" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="J31" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="K31" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="L31" s="2" t="s">
+      <c r="L31" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="M31" s="2">
+      <c r="M31" s="5">
         <v>100</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="N31" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="O31" s="2" t="s">
+      <c r="O31" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="5">
         <v>178</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="5">
         <v>714</v>
       </c>
-      <c r="R31" s="2" t="s">
+      <c r="R31" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="S31" s="4" t="s">
+      <c r="S31" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T31" s="2">
+      <c r="T31" s="1">
         <v>436367</v>
       </c>
     </row>
@@ -3910,152 +4087,176 @@
       <c r="A32" s="1">
         <v>254</v>
       </c>
-      <c r="B32" s="2">
-        <v>1</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="1">
         <v>600</v>
       </c>
       <c r="F32" s="1">
         <v>549</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G32" s="1">
         <v>0</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="I32" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="J32" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="K32" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="L32" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="M32" s="2">
+      <c r="M32" s="1">
         <v>99</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="N32" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="O32" s="2" t="s">
+      <c r="O32" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="P32" s="2">
+      <c r="P32" s="1">
         <v>173</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32" s="1">
         <v>507</v>
       </c>
-      <c r="R32" s="2" t="s">
+      <c r="R32" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="S32" s="4" t="s">
+      <c r="S32" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T32" s="2">
+      <c r="T32" s="1">
         <v>437609</v>
       </c>
     </row>
     <row r="33" spans="1:20">
-      <c r="A33" s="2">
+      <c r="A33" s="1">
         <v>244</v>
       </c>
-      <c r="B33" s="2">
-        <v>1</v>
-      </c>
-      <c r="D33" s="2" t="s">
+      <c r="B33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="1">
         <v>600</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="1">
         <v>510</v>
       </c>
-      <c r="G33" s="2">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2" t="s">
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="I33" s="2" t="s">
+      <c r="I33" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="J33" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="S33" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="T33" s="2" t="s">
+      <c r="K33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T33" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:20">
-      <c r="A34" s="2">
+      <c r="A34" s="1">
         <v>248</v>
       </c>
-      <c r="B34" s="2">
-        <v>1</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="B34" s="1">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="1">
         <v>600</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="1">
         <v>599</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G34" s="1">
         <v>0</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="I34" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="J34" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="K34" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L34" s="2" t="s">
+      <c r="L34" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="M34" s="2">
+      <c r="M34" s="1">
         <v>98</v>
       </c>
-      <c r="N34" s="2" t="s">
+      <c r="N34" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="O34" s="2" t="s">
+      <c r="O34" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
         <v>171</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>737</v>
       </c>
-      <c r="R34" s="2" t="s">
+      <c r="R34" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="S34" s="4" t="s">
+      <c r="S34" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T34" s="2">
+      <c r="T34" s="1">
         <v>440640</v>
       </c>
     </row>
@@ -4066,8 +4267,7 @@
       <c r="B35" s="1">
         <v>1</v>
       </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="7" t="s">
         <v>233</v>
       </c>
       <c r="E35" s="1">
@@ -4097,7 +4297,7 @@
       <c r="M35" s="1">
         <v>100</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="N35" s="8" t="s">
         <v>239</v>
       </c>
       <c r="O35" s="1" t="s">
@@ -4106,16 +4306,16 @@
       <c r="P35" s="1">
         <v>194</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>517</v>
       </c>
-      <c r="R35" s="2" t="s">
+      <c r="R35" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="S35" s="4" t="s">
+      <c r="S35" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T35" s="2">
+      <c r="T35" s="1">
         <v>433586</v>
       </c>
     </row>
@@ -4126,9 +4326,8 @@
       <c r="B36" s="1">
         <v>1</v>
       </c>
-      <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E36" s="1">
         <v>600</v>
@@ -4140,397 +4339,633 @@
         <v>1</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M36" s="1">
         <v>100</v>
       </c>
-      <c r="N36" s="1" t="s">
-        <v>246</v>
+      <c r="N36" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P36" s="1">
         <v>179</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>788</v>
       </c>
-      <c r="R36" s="2" t="s">
+      <c r="R36" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="S36" s="4" t="s">
+      <c r="S36" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T36" s="2">
+      <c r="T36" s="1">
         <v>434593</v>
       </c>
     </row>
     <row r="37" spans="1:20">
-      <c r="A37" s="2">
+      <c r="A37" s="1">
         <v>251</v>
       </c>
-      <c r="B37" s="2">
-        <v>1</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E37" s="2">
+      <c r="B37" s="1">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E37" s="1">
         <v>600</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="1">
         <v>549</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G37" s="1">
         <v>0</v>
       </c>
-      <c r="H37" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="I37" s="2" t="s">
+      <c r="H37" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="I37" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="J37" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="K37" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="M37" s="2">
+      <c r="L37" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="M37" s="1">
         <v>99</v>
       </c>
-      <c r="N37" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="O37" s="2" t="s">
+      <c r="N37" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="P37" s="2">
+      <c r="O37" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="P37" s="1">
         <v>172</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37" s="1">
         <v>818</v>
       </c>
-      <c r="R37" s="2" t="s">
+      <c r="R37" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="S37" s="4" t="s">
+      <c r="S37" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T37" s="2">
+      <c r="T37" s="1">
         <v>439690</v>
       </c>
     </row>
     <row r="38" spans="1:20">
-      <c r="A38" s="2">
+      <c r="A38" s="1">
         <v>251</v>
       </c>
-      <c r="B38" s="2">
-        <v>1</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E38" s="2">
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E38" s="1">
         <v>600</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="1">
         <v>442</v>
       </c>
-      <c r="G38" s="2">
-        <v>1</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="I38" s="2" t="s">
+      <c r="G38" s="1">
+        <v>1</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="I38" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="K38" s="2" t="s">
+      <c r="J38" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="K38" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="M38" s="2">
+      <c r="L38" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="M38" s="1">
         <v>97</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="O38" s="2" t="s">
+      <c r="N38" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="P38" s="2">
+      <c r="O38" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="P38" s="1">
         <v>202</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>784</v>
       </c>
-      <c r="R38" s="2" t="s">
+      <c r="R38" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="S38" s="4" t="s">
+      <c r="S38" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T38" s="2">
+      <c r="T38" s="1">
         <v>443075</v>
       </c>
     </row>
     <row r="39" spans="1:20">
-      <c r="A39" s="2">
+      <c r="A39" s="1">
         <v>261</v>
       </c>
-      <c r="B39" s="2">
-        <v>1</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E39" s="2">
+      <c r="B39" s="1">
+        <v>1</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E39" s="1">
         <v>600</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="1">
         <v>599</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39" s="1">
         <v>0</v>
       </c>
-      <c r="H39" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="I39" s="2" t="s">
+      <c r="H39" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="J39" s="2" t="s">
+      <c r="I39" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="K39" s="2" t="s">
+      <c r="J39" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="L39" s="2" t="s">
+      <c r="K39" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="M39" s="2">
+      <c r="L39" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="M39" s="1">
         <v>94</v>
       </c>
-      <c r="N39" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="O39" s="2" t="s">
+      <c r="N39" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="P39" s="2">
+      <c r="O39" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="P39" s="1">
         <v>229</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>792</v>
       </c>
-      <c r="R39" s="2" t="s">
+      <c r="R39" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="S39" s="4" t="s">
+      <c r="S39" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T39" s="2">
+      <c r="T39" s="1">
         <v>446741</v>
       </c>
     </row>
     <row r="40" spans="1:20">
-      <c r="A40" s="2">
+      <c r="A40" s="1">
         <v>277</v>
       </c>
-      <c r="B40" s="2">
-        <v>1</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E40" s="2">
+      <c r="B40" s="1">
+        <v>1</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E40" s="1">
         <v>600</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="1">
         <v>599</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G40" s="1">
         <v>0</v>
       </c>
-      <c r="H40" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="I40" s="2" t="s">
+      <c r="H40" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="J40" s="2" t="s">
+      <c r="I40" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="L40" s="2" t="s">
+      <c r="K40" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="M40" s="2">
+      <c r="L40" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="M40" s="1">
         <v>68</v>
       </c>
-      <c r="N40" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="O40" s="2" t="s">
+      <c r="N40" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="P40" s="2">
+      <c r="O40" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="P40" s="1">
         <v>229</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>1000</v>
       </c>
-      <c r="R40" s="2" t="s">
+      <c r="R40" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="S40" s="4" t="s">
+      <c r="S40" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T40" s="2">
+      <c r="T40" s="1">
         <v>465889</v>
       </c>
     </row>
     <row r="41" spans="1:20">
-      <c r="A41" s="2">
+      <c r="A41" s="1">
         <v>282</v>
       </c>
-      <c r="B41" s="2">
-        <v>1</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E41" s="2">
+      <c r="B41" s="1">
+        <v>1</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E41" s="1">
         <v>600</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="1">
         <v>599</v>
       </c>
-      <c r="G41" s="2">
+      <c r="G41" s="1">
         <v>0</v>
       </c>
-      <c r="H41" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="I41" s="2" t="s">
+      <c r="H41" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="I41" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K41" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="L41" s="2" t="s">
+      <c r="J41" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="M41" s="2">
+      <c r="K41" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="M41" s="1">
         <v>100</v>
       </c>
-      <c r="N41" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="O41" s="2" t="s">
+      <c r="N41" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="P41" s="2">
+      <c r="O41" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="P41" s="1">
         <v>189</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41" s="1">
         <v>566</v>
       </c>
-      <c r="R41" s="2" t="s">
+      <c r="R41" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="S41" s="4" t="s">
+      <c r="S41" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T41" s="2">
+      <c r="T41" s="1">
         <v>438970</v>
       </c>
     </row>
     <row r="42" spans="1:20">
-      <c r="A42" s="2">
+      <c r="A42" s="1">
         <v>283</v>
       </c>
-      <c r="B42" s="2">
-        <v>1</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E42" s="2">
+      <c r="B42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E42" s="1">
         <v>600</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="1">
         <v>599</v>
       </c>
-      <c r="G42" s="2">
+      <c r="G42" s="1">
         <v>0</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="H42" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="I42" s="2" t="s">
+      <c r="I42" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="M42" s="1">
+        <v>68</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="P42" s="1">
+        <v>238</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>1000</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T42" s="1">
+        <v>465688</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
+      <c r="A43" s="1">
         <v>285</v>
       </c>
-      <c r="J42" s="2" t="s">
+      <c r="B43" s="1">
+        <v>1</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E43" s="1">
+        <v>600</v>
+      </c>
+      <c r="F43" s="1">
+        <v>599</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="M43" s="1">
+        <v>100</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="P43" s="1">
+        <v>187</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>607</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T43" s="1">
+        <v>436296</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
+      <c r="A44" s="1">
         <v>286</v>
       </c>
-      <c r="K42" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L42" s="2" t="s">
+      <c r="B44" s="1">
+        <v>1</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E44" s="1">
+        <v>600</v>
+      </c>
+      <c r="F44" s="1">
+        <v>599</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="M44" s="1">
+        <v>93</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="P44" s="1">
+        <v>191</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>803</v>
+      </c>
+      <c r="R44" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T44" s="1">
+        <v>443500</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
+      <c r="A45" s="1">
         <v>288</v>
       </c>
-      <c r="M42" s="2">
-        <v>68</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="P42" s="2">
-        <v>238</v>
-      </c>
-      <c r="Q42" s="2">
-        <v>1000</v>
-      </c>
-      <c r="R42" s="2" t="s">
+      <c r="B45" s="1">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E45" s="1">
+        <v>600</v>
+      </c>
+      <c r="F45" s="1">
+        <v>599</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="M45" s="1">
+        <v>100</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="P45" s="6">
+        <v>168</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>473</v>
+      </c>
+      <c r="R45" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="S42" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="T42" s="2">
-        <v>465688</v>
+      <c r="S45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T45" s="1">
+        <v>435230</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20">
+      <c r="A46" s="1">
+        <v>288</v>
+      </c>
+      <c r="B46" s="1">
+        <v>1</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E46" s="1">
+        <v>600</v>
+      </c>
+      <c r="F46" s="1">
+        <v>599</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="M46" s="1">
+        <v>99</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="P46" s="1">
+        <v>171</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>874</v>
+      </c>
+      <c r="R46" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T46" s="1">
+        <v>439228</v>
       </c>
     </row>
   </sheetData>
